--- a/Grout Stats/CI-PRO-001_REG-001 ROTURA DE GROUT 005.xlsx
+++ b/Grout Stats/CI-PRO-001_REG-001 ROTURA DE GROUT 005.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Powerchina\Tecnopilotes\Registros de Calidad\05 AG-08 (22-12-25)\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1217563E-871D-40FA-B1E9-A858C94BAF57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E46BA9D-71BC-4EB4-A776-E15FC5ACA11F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -166,18 +166,6 @@
 INFORME N°: 05</t>
   </si>
   <si>
-    <t>TE-0107</t>
-  </si>
-  <si>
-    <t>TE-0108</t>
-  </si>
-  <si>
-    <t>TE-0109</t>
-  </si>
-  <si>
-    <t>TE-0110</t>
-  </si>
-  <si>
     <t>TE-117</t>
   </si>
   <si>
@@ -251,6 +239,18 @@
       </rPr>
       <t>1) Los valores en rojo son desechados por estar por encima o por debajo del promedio +- la desv standard del grupo de muestreo.</t>
     </r>
+  </si>
+  <si>
+    <t>TE-107</t>
+  </si>
+  <si>
+    <t>TE-108</t>
+  </si>
+  <si>
+    <t>TE-109</t>
+  </si>
+  <si>
+    <t>TE-110</t>
   </si>
 </sst>
 </file>
@@ -980,168 +980,6 @@
     <xf numFmtId="4" fontId="12" fillId="6" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="distributed"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="distributed"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="distributed"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="distributed"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="distributed"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="distributed"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="distributed" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="distributed"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="distributed"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="distributed"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="distributed" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="distributed" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="distributed" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="distributed"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="distributed"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="distributed"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="distributed"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="distributed"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="distributed"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="distributed"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="distributed"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="distributed"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="14" fontId="1" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="distributed"/>
     </xf>
@@ -1161,23 +999,185 @@
     <xf numFmtId="4" fontId="13" fillId="5" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="distributed"/>
     </xf>
+    <xf numFmtId="10" fontId="12" fillId="5" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="distributed"/>
+    </xf>
+    <xf numFmtId="10" fontId="12" fillId="6" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="distributed"/>
+    </xf>
+    <xf numFmtId="10" fontId="12" fillId="0" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="distributed"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="distributed"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="distributed"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="distributed"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="distributed"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="distributed"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="distributed"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="distributed" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="distributed"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="distributed"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="distributed"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="distributed" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="distributed" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="distributed" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="distributed"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="distributed"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="distributed"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="10" fontId="12" fillId="5" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="distributed"/>
-    </xf>
-    <xf numFmtId="10" fontId="12" fillId="6" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="distributed"/>
-    </xf>
-    <xf numFmtId="10" fontId="12" fillId="0" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="distributed"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="distributed"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="distributed"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="distributed"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="distributed"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="distributed"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1786,178 +1786,178 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:20" ht="24.75" customHeight="1">
-      <c r="A1" s="51" t="s">
+      <c r="A1" s="62" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="52"/>
-      <c r="C1" s="52"/>
-      <c r="D1" s="68" t="s">
+      <c r="B1" s="63"/>
+      <c r="C1" s="63"/>
+      <c r="D1" s="82" t="s">
         <v>25</v>
       </c>
-      <c r="E1" s="69"/>
-      <c r="F1" s="69"/>
-      <c r="G1" s="69"/>
-      <c r="H1" s="69"/>
-      <c r="I1" s="69"/>
-      <c r="J1" s="69"/>
-      <c r="K1" s="69"/>
-      <c r="L1" s="69"/>
-      <c r="M1" s="70"/>
-      <c r="N1" s="76" t="s">
+      <c r="E1" s="83"/>
+      <c r="F1" s="83"/>
+      <c r="G1" s="83"/>
+      <c r="H1" s="83"/>
+      <c r="I1" s="83"/>
+      <c r="J1" s="83"/>
+      <c r="K1" s="83"/>
+      <c r="L1" s="83"/>
+      <c r="M1" s="84"/>
+      <c r="N1" s="91" t="s">
         <v>26</v>
       </c>
-      <c r="O1" s="77"/>
+      <c r="O1" s="92"/>
     </row>
     <row r="2" spans="1:20" ht="28.5" customHeight="1">
-      <c r="A2" s="53"/>
-      <c r="B2" s="54"/>
-      <c r="C2" s="54"/>
-      <c r="D2" s="71"/>
-      <c r="E2" s="100"/>
-      <c r="F2" s="100"/>
-      <c r="G2" s="100"/>
-      <c r="H2" s="100"/>
-      <c r="I2" s="100"/>
-      <c r="J2" s="100"/>
-      <c r="K2" s="100"/>
-      <c r="L2" s="100"/>
-      <c r="M2" s="72"/>
-      <c r="N2" s="78"/>
-      <c r="O2" s="79"/>
+      <c r="A2" s="64"/>
+      <c r="B2" s="65"/>
+      <c r="C2" s="65"/>
+      <c r="D2" s="85"/>
+      <c r="E2" s="86"/>
+      <c r="F2" s="86"/>
+      <c r="G2" s="86"/>
+      <c r="H2" s="86"/>
+      <c r="I2" s="86"/>
+      <c r="J2" s="86"/>
+      <c r="K2" s="86"/>
+      <c r="L2" s="86"/>
+      <c r="M2" s="87"/>
+      <c r="N2" s="93"/>
+      <c r="O2" s="94"/>
     </row>
     <row r="3" spans="1:20" ht="43.5" customHeight="1">
-      <c r="A3" s="53"/>
-      <c r="B3" s="54"/>
-      <c r="C3" s="54"/>
-      <c r="D3" s="73"/>
-      <c r="E3" s="74"/>
-      <c r="F3" s="74"/>
-      <c r="G3" s="74"/>
-      <c r="H3" s="74"/>
-      <c r="I3" s="74"/>
-      <c r="J3" s="74"/>
-      <c r="K3" s="74"/>
-      <c r="L3" s="74"/>
-      <c r="M3" s="75"/>
-      <c r="N3" s="78"/>
-      <c r="O3" s="79"/>
+      <c r="A3" s="64"/>
+      <c r="B3" s="65"/>
+      <c r="C3" s="65"/>
+      <c r="D3" s="88"/>
+      <c r="E3" s="89"/>
+      <c r="F3" s="89"/>
+      <c r="G3" s="89"/>
+      <c r="H3" s="89"/>
+      <c r="I3" s="89"/>
+      <c r="J3" s="89"/>
+      <c r="K3" s="89"/>
+      <c r="L3" s="89"/>
+      <c r="M3" s="90"/>
+      <c r="N3" s="93"/>
+      <c r="O3" s="94"/>
     </row>
     <row r="4" spans="1:20" ht="35.25" customHeight="1">
-      <c r="A4" s="44" t="s">
+      <c r="A4" s="95" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="45"/>
-      <c r="C4" s="46" t="s">
-        <v>37</v>
-      </c>
-      <c r="D4" s="47"/>
-      <c r="E4" s="47"/>
-      <c r="F4" s="47"/>
-      <c r="G4" s="47"/>
-      <c r="H4" s="47"/>
-      <c r="I4" s="47"/>
-      <c r="J4" s="47"/>
-      <c r="K4" s="47"/>
-      <c r="L4" s="47"/>
-      <c r="M4" s="47"/>
-      <c r="N4" s="47"/>
-      <c r="O4" s="48"/>
+      <c r="B4" s="96"/>
+      <c r="C4" s="97" t="s">
+        <v>33</v>
+      </c>
+      <c r="D4" s="98"/>
+      <c r="E4" s="98"/>
+      <c r="F4" s="98"/>
+      <c r="G4" s="98"/>
+      <c r="H4" s="98"/>
+      <c r="I4" s="98"/>
+      <c r="J4" s="98"/>
+      <c r="K4" s="98"/>
+      <c r="L4" s="98"/>
+      <c r="M4" s="98"/>
+      <c r="N4" s="98"/>
+      <c r="O4" s="99"/>
     </row>
     <row r="5" spans="1:20" ht="34.5" customHeight="1" thickBot="1">
-      <c r="A5" s="49" t="s">
+      <c r="A5" s="100" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="50"/>
-      <c r="C5" s="50"/>
-      <c r="D5" s="50"/>
-      <c r="E5" s="50"/>
-      <c r="F5" s="62" t="s">
+      <c r="B5" s="101"/>
+      <c r="C5" s="101"/>
+      <c r="D5" s="101"/>
+      <c r="E5" s="101"/>
+      <c r="F5" s="76" t="s">
         <v>24</v>
       </c>
-      <c r="G5" s="63"/>
-      <c r="H5" s="63"/>
-      <c r="I5" s="63"/>
-      <c r="J5" s="63"/>
-      <c r="K5" s="63"/>
-      <c r="L5" s="64"/>
-      <c r="M5" s="65" t="s">
+      <c r="G5" s="77"/>
+      <c r="H5" s="77"/>
+      <c r="I5" s="77"/>
+      <c r="J5" s="77"/>
+      <c r="K5" s="77"/>
+      <c r="L5" s="78"/>
+      <c r="M5" s="79" t="s">
         <v>9</v>
       </c>
-      <c r="N5" s="66"/>
-      <c r="O5" s="67"/>
+      <c r="N5" s="80"/>
+      <c r="O5" s="81"/>
     </row>
     <row r="6" spans="1:20" ht="28.5" customHeight="1">
-      <c r="A6" s="42" t="s">
+      <c r="A6" s="74" t="s">
         <v>1</v>
       </c>
-      <c r="B6" s="42" t="s">
+      <c r="B6" s="74" t="s">
         <v>10</v>
       </c>
-      <c r="C6" s="38" t="s">
+      <c r="C6" s="102" t="s">
         <v>11</v>
       </c>
-      <c r="D6" s="39"/>
-      <c r="E6" s="42" t="s">
+      <c r="D6" s="103"/>
+      <c r="E6" s="74" t="s">
         <v>12</v>
       </c>
-      <c r="F6" s="42" t="s">
+      <c r="F6" s="74" t="s">
         <v>13</v>
       </c>
-      <c r="G6" s="42" t="s">
+      <c r="G6" s="74" t="s">
         <v>14</v>
       </c>
-      <c r="H6" s="42" t="s">
+      <c r="H6" s="74" t="s">
         <v>15</v>
       </c>
-      <c r="I6" s="42" t="s">
+      <c r="I6" s="74" t="s">
         <v>19</v>
       </c>
-      <c r="J6" s="42" t="s">
+      <c r="J6" s="74" t="s">
         <v>18</v>
       </c>
-      <c r="K6" s="42" t="s">
+      <c r="K6" s="74" t="s">
         <v>20</v>
       </c>
-      <c r="L6" s="42" t="s">
+      <c r="L6" s="74" t="s">
         <v>16</v>
       </c>
-      <c r="M6" s="42" t="s">
+      <c r="M6" s="74" t="s">
         <v>21</v>
       </c>
-      <c r="N6" s="42" t="s">
+      <c r="N6" s="74" t="s">
         <v>22</v>
       </c>
-      <c r="O6" s="42" t="s">
+      <c r="O6" s="74" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="7" spans="1:20" ht="36.75" customHeight="1" thickBot="1">
-      <c r="A7" s="43"/>
-      <c r="B7" s="43"/>
-      <c r="C7" s="40"/>
-      <c r="D7" s="41"/>
-      <c r="E7" s="43"/>
-      <c r="F7" s="43"/>
-      <c r="G7" s="43"/>
-      <c r="H7" s="43"/>
-      <c r="I7" s="43"/>
-      <c r="J7" s="43"/>
-      <c r="K7" s="43"/>
-      <c r="L7" s="43"/>
-      <c r="M7" s="43"/>
-      <c r="N7" s="43"/>
-      <c r="O7" s="43"/>
+      <c r="A7" s="75"/>
+      <c r="B7" s="75"/>
+      <c r="C7" s="104"/>
+      <c r="D7" s="105"/>
+      <c r="E7" s="75"/>
+      <c r="F7" s="75"/>
+      <c r="G7" s="75"/>
+      <c r="H7" s="75"/>
+      <c r="I7" s="75"/>
+      <c r="J7" s="75"/>
+      <c r="K7" s="75"/>
+      <c r="L7" s="75"/>
+      <c r="M7" s="75"/>
+      <c r="N7" s="75"/>
+      <c r="O7" s="75"/>
       <c r="Q7" s="5" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="R7" s="5" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="S7" s="5" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="T7" s="5" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
     </row>
     <row r="8" spans="1:20" ht="39.75" customHeight="1">
@@ -1965,12 +1965,12 @@
         <v>1</v>
       </c>
       <c r="B8" s="24" t="s">
-        <v>27</v>
-      </c>
-      <c r="C8" s="80" t="s">
-        <v>36</v>
-      </c>
-      <c r="D8" s="81"/>
+        <v>48</v>
+      </c>
+      <c r="C8" s="50" t="s">
+        <v>32</v>
+      </c>
+      <c r="D8" s="51"/>
       <c r="E8" s="24" t="s">
         <v>17</v>
       </c>
@@ -2003,11 +2003,11 @@
         <f>+(M8*1000)/(I8*J8)</f>
         <v>83.84</v>
       </c>
-      <c r="O8" s="101">
+      <c r="O8" s="45">
         <f>+N8/100</f>
         <v>0.83840000000000003</v>
       </c>
-      <c r="Q8" s="95">
+      <c r="Q8" s="41">
         <f>+AVERAGE(N8:N11)</f>
         <v>83.83</v>
       </c>
@@ -2015,11 +2015,11 @@
         <f>+STDEVA(N8:N11)</f>
         <v>3.3268804206543585</v>
       </c>
-      <c r="S8" s="95">
+      <c r="S8" s="41">
         <f>+Q8-R8</f>
         <v>80.503119579345636</v>
       </c>
-      <c r="T8" s="95">
+      <c r="T8" s="41">
         <f>+Q8+R8</f>
         <v>87.15688042065436</v>
       </c>
@@ -2029,12 +2029,12 @@
         <v>2</v>
       </c>
       <c r="B9" s="24" t="s">
-        <v>28</v>
-      </c>
-      <c r="C9" s="80" t="s">
-        <v>36</v>
-      </c>
-      <c r="D9" s="81"/>
+        <v>49</v>
+      </c>
+      <c r="C9" s="50" t="s">
+        <v>32</v>
+      </c>
+      <c r="D9" s="51"/>
       <c r="E9" s="24" t="s">
         <v>17</v>
       </c>
@@ -2067,7 +2067,7 @@
         <f t="shared" ref="N9:N21" si="1">+(M9*1000)/(I9*J9)</f>
         <v>85.4</v>
       </c>
-      <c r="O9" s="101">
+      <c r="O9" s="45">
         <f t="shared" ref="O9:O21" si="2">+N9/100</f>
         <v>0.85400000000000009</v>
       </c>
@@ -2077,12 +2077,12 @@
         <v>3</v>
       </c>
       <c r="B10" s="24" t="s">
-        <v>29</v>
-      </c>
-      <c r="C10" s="80" t="s">
-        <v>36</v>
-      </c>
-      <c r="D10" s="81"/>
+        <v>50</v>
+      </c>
+      <c r="C10" s="50" t="s">
+        <v>32</v>
+      </c>
+      <c r="D10" s="51"/>
       <c r="E10" s="24" t="s">
         <v>17</v>
       </c>
@@ -2111,11 +2111,11 @@
       <c r="M10" s="36">
         <v>198</v>
       </c>
-      <c r="N10" s="96">
+      <c r="N10" s="42">
         <f t="shared" si="1"/>
         <v>79.2</v>
       </c>
-      <c r="O10" s="101">
+      <c r="O10" s="45">
         <f t="shared" si="2"/>
         <v>0.79200000000000004</v>
       </c>
@@ -2125,12 +2125,12 @@
         <v>4</v>
       </c>
       <c r="B11" s="24" t="s">
-        <v>30</v>
-      </c>
-      <c r="C11" s="80" t="s">
-        <v>36</v>
-      </c>
-      <c r="D11" s="81"/>
+        <v>51</v>
+      </c>
+      <c r="C11" s="50" t="s">
+        <v>32</v>
+      </c>
+      <c r="D11" s="51"/>
       <c r="E11" s="24" t="s">
         <v>17</v>
       </c>
@@ -2163,21 +2163,21 @@
         <f t="shared" si="1"/>
         <v>86.88</v>
       </c>
-      <c r="O11" s="101">
+      <c r="O11" s="45">
         <f t="shared" si="2"/>
         <v>0.86879999999999991</v>
       </c>
       <c r="Q11" s="5" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="R11" s="5" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="S11" s="5" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="T11" s="5" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
     </row>
     <row r="12" spans="1:20" ht="39.75" customHeight="1">
@@ -2185,12 +2185,12 @@
         <v>5</v>
       </c>
       <c r="B12" s="30" t="s">
-        <v>31</v>
-      </c>
-      <c r="C12" s="84" t="s">
-        <v>36</v>
-      </c>
-      <c r="D12" s="85"/>
+        <v>27</v>
+      </c>
+      <c r="C12" s="54" t="s">
+        <v>32</v>
+      </c>
+      <c r="D12" s="55"/>
       <c r="E12" s="30" t="s">
         <v>17</v>
       </c>
@@ -2223,11 +2223,11 @@
         <f t="shared" si="1"/>
         <v>112</v>
       </c>
-      <c r="O12" s="102">
+      <c r="O12" s="46">
         <f t="shared" si="2"/>
         <v>1.1200000000000001</v>
       </c>
-      <c r="Q12" s="95">
+      <c r="Q12" s="41">
         <f>+AVERAGE(N12:N16)</f>
         <v>106.2</v>
       </c>
@@ -2235,11 +2235,11 @@
         <f>+STDEVA(N12:N16)</f>
         <v>10.208349523796681</v>
       </c>
-      <c r="S12" s="95">
+      <c r="S12" s="41">
         <f>+Q12-R12</f>
         <v>95.991650476203318</v>
       </c>
-      <c r="T12" s="95">
+      <c r="T12" s="41">
         <f>+Q12+R12</f>
         <v>116.40834952379669</v>
       </c>
@@ -2249,12 +2249,12 @@
         <v>6</v>
       </c>
       <c r="B13" s="30" t="s">
+        <v>28</v>
+      </c>
+      <c r="C13" s="54" t="s">
         <v>32</v>
       </c>
-      <c r="C13" s="84" t="s">
-        <v>36</v>
-      </c>
-      <c r="D13" s="85"/>
+      <c r="D13" s="55"/>
       <c r="E13" s="30" t="s">
         <v>17</v>
       </c>
@@ -2287,7 +2287,7 @@
         <f t="shared" si="1"/>
         <v>103.68</v>
       </c>
-      <c r="O13" s="102">
+      <c r="O13" s="46">
         <f t="shared" si="2"/>
         <v>1.0368000000000002</v>
       </c>
@@ -2297,12 +2297,12 @@
         <v>7</v>
       </c>
       <c r="B14" s="30" t="s">
-        <v>33</v>
-      </c>
-      <c r="C14" s="84" t="s">
-        <v>36</v>
-      </c>
-      <c r="D14" s="85"/>
+        <v>29</v>
+      </c>
+      <c r="C14" s="54" t="s">
+        <v>32</v>
+      </c>
+      <c r="D14" s="55"/>
       <c r="E14" s="30" t="s">
         <v>17</v>
       </c>
@@ -2331,11 +2331,11 @@
       <c r="M14" s="35">
         <v>226.9</v>
       </c>
-      <c r="N14" s="97">
+      <c r="N14" s="43">
         <f t="shared" si="1"/>
         <v>90.76</v>
       </c>
-      <c r="O14" s="102">
+      <c r="O14" s="46">
         <f t="shared" si="2"/>
         <v>0.90760000000000007</v>
       </c>
@@ -2345,12 +2345,12 @@
         <v>8</v>
       </c>
       <c r="B15" s="30" t="s">
-        <v>34</v>
-      </c>
-      <c r="C15" s="84" t="s">
-        <v>36</v>
-      </c>
-      <c r="D15" s="85"/>
+        <v>30</v>
+      </c>
+      <c r="C15" s="54" t="s">
+        <v>32</v>
+      </c>
+      <c r="D15" s="55"/>
       <c r="E15" s="30" t="s">
         <v>17</v>
       </c>
@@ -2379,11 +2379,11 @@
       <c r="M15" s="35">
         <v>294.89999999999998</v>
       </c>
-      <c r="N15" s="97">
+      <c r="N15" s="43">
         <f t="shared" si="1"/>
         <v>117.96</v>
       </c>
-      <c r="O15" s="102">
+      <c r="O15" s="46">
         <f t="shared" si="2"/>
         <v>1.1796</v>
       </c>
@@ -2393,12 +2393,12 @@
         <v>9</v>
       </c>
       <c r="B16" s="30" t="s">
-        <v>35</v>
-      </c>
-      <c r="C16" s="84" t="s">
-        <v>36</v>
-      </c>
-      <c r="D16" s="85"/>
+        <v>31</v>
+      </c>
+      <c r="C16" s="54" t="s">
+        <v>32</v>
+      </c>
+      <c r="D16" s="55"/>
       <c r="E16" s="30" t="s">
         <v>17</v>
       </c>
@@ -2431,21 +2431,21 @@
         <f t="shared" si="1"/>
         <v>106.6</v>
       </c>
-      <c r="O16" s="102">
+      <c r="O16" s="46">
         <f t="shared" si="2"/>
         <v>1.0659999999999998</v>
       </c>
       <c r="Q16" s="5" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="R16" s="5" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="S16" s="5" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="T16" s="5" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
     </row>
     <row r="17" spans="1:20" ht="39.75" customHeight="1">
@@ -2453,19 +2453,19 @@
         <v>10</v>
       </c>
       <c r="B17" s="24" t="s">
-        <v>38</v>
-      </c>
-      <c r="C17" s="80" t="s">
-        <v>36</v>
-      </c>
-      <c r="D17" s="81"/>
+        <v>34</v>
+      </c>
+      <c r="C17" s="50" t="s">
+        <v>32</v>
+      </c>
+      <c r="D17" s="51"/>
       <c r="E17" s="24" t="s">
         <v>17</v>
       </c>
       <c r="F17" s="25">
         <v>46013</v>
       </c>
-      <c r="G17" s="92">
+      <c r="G17" s="38">
         <v>46041</v>
       </c>
       <c r="H17" s="26">
@@ -2484,18 +2484,18 @@
       <c r="L17" s="27">
         <v>331</v>
       </c>
-      <c r="M17" s="93">
+      <c r="M17" s="39">
         <v>317.60000000000002</v>
       </c>
-      <c r="N17" s="94">
+      <c r="N17" s="40">
         <f t="shared" si="1"/>
         <v>127.04</v>
       </c>
-      <c r="O17" s="101">
+      <c r="O17" s="45">
         <f t="shared" si="2"/>
         <v>1.2704</v>
       </c>
-      <c r="Q17" s="95">
+      <c r="Q17" s="41">
         <f>+AVERAGE(N17:N21)</f>
         <v>122.28800000000001</v>
       </c>
@@ -2503,11 +2503,11 @@
         <f>+STDEVA(N17:N21)</f>
         <v>9.5987665874319497</v>
       </c>
-      <c r="S17" s="95">
+      <c r="S17" s="41">
         <f>+Q17-R17</f>
         <v>112.68923341256806</v>
       </c>
-      <c r="T17" s="95">
+      <c r="T17" s="41">
         <f>+Q17+R17</f>
         <v>131.88676658743196</v>
       </c>
@@ -2517,19 +2517,19 @@
         <v>11</v>
       </c>
       <c r="B18" s="24" t="s">
+        <v>35</v>
+      </c>
+      <c r="C18" s="50" t="s">
+        <v>32</v>
+      </c>
+      <c r="D18" s="51"/>
+      <c r="E18" s="24" t="s">
         <v>39</v>
-      </c>
-      <c r="C18" s="80" t="s">
-        <v>36</v>
-      </c>
-      <c r="D18" s="81"/>
-      <c r="E18" s="24" t="s">
-        <v>43</v>
       </c>
       <c r="F18" s="25">
         <v>46013</v>
       </c>
-      <c r="G18" s="92">
+      <c r="G18" s="38">
         <v>46041</v>
       </c>
       <c r="H18" s="26">
@@ -2548,14 +2548,14 @@
       <c r="L18" s="27">
         <v>324</v>
       </c>
-      <c r="M18" s="93">
+      <c r="M18" s="39">
         <v>306.60000000000002</v>
       </c>
-      <c r="N18" s="94">
+      <c r="N18" s="40">
         <f t="shared" si="1"/>
         <v>122.64</v>
       </c>
-      <c r="O18" s="101">
+      <c r="O18" s="45">
         <f t="shared" si="2"/>
         <v>1.2263999999999999</v>
       </c>
@@ -2565,19 +2565,19 @@
         <v>12</v>
       </c>
       <c r="B19" s="24" t="s">
+        <v>36</v>
+      </c>
+      <c r="C19" s="50" t="s">
+        <v>32</v>
+      </c>
+      <c r="D19" s="51"/>
+      <c r="E19" s="24" t="s">
         <v>40</v>
-      </c>
-      <c r="C19" s="80" t="s">
-        <v>36</v>
-      </c>
-      <c r="D19" s="81"/>
-      <c r="E19" s="24" t="s">
-        <v>44</v>
       </c>
       <c r="F19" s="25">
         <v>46013</v>
       </c>
-      <c r="G19" s="92">
+      <c r="G19" s="38">
         <v>46041</v>
       </c>
       <c r="H19" s="26">
@@ -2596,14 +2596,14 @@
       <c r="L19" s="27">
         <v>325</v>
       </c>
-      <c r="M19" s="93">
+      <c r="M19" s="39">
         <v>265</v>
       </c>
-      <c r="N19" s="98">
+      <c r="N19" s="44">
         <f t="shared" si="1"/>
         <v>106</v>
       </c>
-      <c r="O19" s="101">
+      <c r="O19" s="45">
         <f t="shared" si="2"/>
         <v>1.06</v>
       </c>
@@ -2613,19 +2613,19 @@
         <v>13</v>
       </c>
       <c r="B20" s="24" t="s">
+        <v>37</v>
+      </c>
+      <c r="C20" s="50" t="s">
+        <v>32</v>
+      </c>
+      <c r="D20" s="51"/>
+      <c r="E20" s="24" t="s">
         <v>41</v>
-      </c>
-      <c r="C20" s="80" t="s">
-        <v>36</v>
-      </c>
-      <c r="D20" s="81"/>
-      <c r="E20" s="24" t="s">
-        <v>45</v>
       </c>
       <c r="F20" s="25">
         <v>46013</v>
       </c>
-      <c r="G20" s="92">
+      <c r="G20" s="38">
         <v>46041</v>
       </c>
       <c r="H20" s="26">
@@ -2644,14 +2644,14 @@
       <c r="L20" s="27">
         <v>327</v>
       </c>
-      <c r="M20" s="93">
+      <c r="M20" s="39">
         <v>327.2</v>
       </c>
-      <c r="N20" s="94">
+      <c r="N20" s="40">
         <f t="shared" si="1"/>
         <v>130.88</v>
       </c>
-      <c r="O20" s="101">
+      <c r="O20" s="45">
         <f t="shared" si="2"/>
         <v>1.3088</v>
       </c>
@@ -2661,19 +2661,19 @@
         <v>14</v>
       </c>
       <c r="B21" s="24" t="s">
+        <v>38</v>
+      </c>
+      <c r="C21" s="50" t="s">
+        <v>32</v>
+      </c>
+      <c r="D21" s="51"/>
+      <c r="E21" s="24" t="s">
         <v>42</v>
-      </c>
-      <c r="C21" s="80" t="s">
-        <v>36</v>
-      </c>
-      <c r="D21" s="81"/>
-      <c r="E21" s="24" t="s">
-        <v>46</v>
       </c>
       <c r="F21" s="25">
         <v>46013</v>
       </c>
-      <c r="G21" s="92">
+      <c r="G21" s="38">
         <v>46041</v>
       </c>
       <c r="H21" s="26">
@@ -2692,14 +2692,14 @@
       <c r="L21" s="27">
         <v>324</v>
       </c>
-      <c r="M21" s="93">
+      <c r="M21" s="39">
         <v>312.2</v>
       </c>
-      <c r="N21" s="94">
+      <c r="N21" s="40">
         <f t="shared" si="1"/>
         <v>124.88</v>
       </c>
-      <c r="O21" s="101">
+      <c r="O21" s="45">
         <f t="shared" si="2"/>
         <v>1.2487999999999999</v>
       </c>
@@ -2707,8 +2707,8 @@
     <row r="22" spans="1:20" ht="39.75" customHeight="1">
       <c r="A22" s="3"/>
       <c r="B22" s="4"/>
-      <c r="C22" s="82"/>
-      <c r="D22" s="83"/>
+      <c r="C22" s="52"/>
+      <c r="D22" s="53"/>
       <c r="E22" s="4"/>
       <c r="F22" s="4"/>
       <c r="G22" s="4"/>
@@ -2719,13 +2719,13 @@
       <c r="L22" s="15"/>
       <c r="M22" s="16"/>
       <c r="N22" s="17"/>
-      <c r="O22" s="103"/>
+      <c r="O22" s="47"/>
     </row>
     <row r="23" spans="1:20" ht="39.75" customHeight="1" thickBot="1">
       <c r="A23" s="3"/>
       <c r="B23" s="4"/>
-      <c r="C23" s="82"/>
-      <c r="D23" s="83"/>
+      <c r="C23" s="52"/>
+      <c r="D23" s="53"/>
       <c r="E23" s="21"/>
       <c r="F23" s="4"/>
       <c r="G23" s="4"/>
@@ -2736,64 +2736,64 @@
       <c r="L23" s="15"/>
       <c r="M23" s="16"/>
       <c r="N23" s="17"/>
-      <c r="O23" s="103"/>
+      <c r="O23" s="47"/>
     </row>
     <row r="24" spans="1:20" ht="39.75" customHeight="1">
-      <c r="A24" s="99" t="s">
-        <v>51</v>
-      </c>
-      <c r="B24" s="55"/>
-      <c r="C24" s="55"/>
-      <c r="D24" s="55"/>
-      <c r="E24" s="55"/>
-      <c r="F24" s="55"/>
-      <c r="G24" s="55"/>
-      <c r="H24" s="55"/>
-      <c r="I24" s="55"/>
-      <c r="J24" s="55"/>
-      <c r="K24" s="55"/>
-      <c r="L24" s="55"/>
-      <c r="M24" s="56"/>
-      <c r="N24" s="56"/>
-      <c r="O24" s="57"/>
+      <c r="A24" s="66" t="s">
+        <v>47</v>
+      </c>
+      <c r="B24" s="67"/>
+      <c r="C24" s="67"/>
+      <c r="D24" s="67"/>
+      <c r="E24" s="67"/>
+      <c r="F24" s="67"/>
+      <c r="G24" s="67"/>
+      <c r="H24" s="67"/>
+      <c r="I24" s="67"/>
+      <c r="J24" s="67"/>
+      <c r="K24" s="67"/>
+      <c r="L24" s="67"/>
+      <c r="M24" s="68"/>
+      <c r="N24" s="68"/>
+      <c r="O24" s="69"/>
     </row>
     <row r="25" spans="1:20" ht="30" customHeight="1" thickBot="1">
-      <c r="A25" s="58"/>
-      <c r="B25" s="59"/>
-      <c r="C25" s="59"/>
-      <c r="D25" s="59"/>
-      <c r="E25" s="59"/>
-      <c r="F25" s="59"/>
-      <c r="G25" s="59"/>
-      <c r="H25" s="59"/>
-      <c r="I25" s="59"/>
-      <c r="J25" s="59"/>
-      <c r="K25" s="59"/>
-      <c r="L25" s="59"/>
-      <c r="M25" s="60"/>
-      <c r="N25" s="60"/>
-      <c r="O25" s="61"/>
+      <c r="A25" s="70"/>
+      <c r="B25" s="71"/>
+      <c r="C25" s="71"/>
+      <c r="D25" s="71"/>
+      <c r="E25" s="71"/>
+      <c r="F25" s="71"/>
+      <c r="G25" s="71"/>
+      <c r="H25" s="71"/>
+      <c r="I25" s="71"/>
+      <c r="J25" s="71"/>
+      <c r="K25" s="71"/>
+      <c r="L25" s="71"/>
+      <c r="M25" s="72"/>
+      <c r="N25" s="72"/>
+      <c r="O25" s="73"/>
     </row>
     <row r="26" spans="1:20" s="1" customFormat="1" ht="30" customHeight="1" thickBot="1">
-      <c r="A26" s="89" t="s">
+      <c r="A26" s="59" t="s">
         <v>2</v>
       </c>
-      <c r="B26" s="90"/>
-      <c r="C26" s="90"/>
-      <c r="D26" s="90"/>
-      <c r="E26" s="90"/>
-      <c r="F26" s="90"/>
-      <c r="G26" s="90"/>
-      <c r="H26" s="90"/>
-      <c r="I26" s="91"/>
-      <c r="J26" s="86" t="s">
+      <c r="B26" s="60"/>
+      <c r="C26" s="60"/>
+      <c r="D26" s="60"/>
+      <c r="E26" s="60"/>
+      <c r="F26" s="60"/>
+      <c r="G26" s="60"/>
+      <c r="H26" s="60"/>
+      <c r="I26" s="61"/>
+      <c r="J26" s="56" t="s">
         <v>3</v>
       </c>
-      <c r="K26" s="87"/>
-      <c r="L26" s="87"/>
-      <c r="M26" s="87"/>
-      <c r="N26" s="87"/>
-      <c r="O26" s="88"/>
+      <c r="K26" s="57"/>
+      <c r="L26" s="57"/>
+      <c r="M26" s="57"/>
+      <c r="N26" s="57"/>
+      <c r="O26" s="58"/>
       <c r="P26" s="14"/>
       <c r="Q26" s="14"/>
     </row>
@@ -2801,17 +2801,17 @@
       <c r="A27" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="B27" s="104"/>
+      <c r="B27" s="48"/>
       <c r="C27" s="9"/>
       <c r="D27" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="E27" s="104"/>
+      <c r="E27" s="48"/>
       <c r="F27" s="9"/>
       <c r="G27" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="H27" s="105"/>
+      <c r="H27" s="49"/>
       <c r="I27" s="6"/>
       <c r="J27" s="8" t="s">
         <v>4</v>
@@ -2832,17 +2832,17 @@
       <c r="A28" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="B28" s="104"/>
+      <c r="B28" s="48"/>
       <c r="C28" s="9"/>
       <c r="D28" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="E28" s="104"/>
+      <c r="E28" s="48"/>
       <c r="F28" s="9"/>
       <c r="G28" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="H28" s="105"/>
+      <c r="H28" s="49"/>
       <c r="I28" s="6"/>
       <c r="J28" s="8" t="s">
         <v>5</v>
@@ -2895,21 +2895,16 @@
     <filterColumn colId="12" showButton="0"/>
   </autoFilter>
   <mergeCells count="41">
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="J26:O26"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="A26:I26"/>
+    <mergeCell ref="N6:N7"/>
+    <mergeCell ref="G6:G7"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="C4:O4"/>
+    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="C6:D7"/>
+    <mergeCell ref="E6:E7"/>
+    <mergeCell ref="J6:J7"/>
+    <mergeCell ref="F6:F7"/>
+    <mergeCell ref="M6:M7"/>
     <mergeCell ref="A1:C3"/>
     <mergeCell ref="A24:O25"/>
     <mergeCell ref="A6:A7"/>
@@ -2926,16 +2921,21 @@
     <mergeCell ref="C8:D8"/>
     <mergeCell ref="C9:D9"/>
     <mergeCell ref="C10:D10"/>
-    <mergeCell ref="N6:N7"/>
-    <mergeCell ref="G6:G7"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="C4:O4"/>
-    <mergeCell ref="A5:E5"/>
-    <mergeCell ref="C6:D7"/>
-    <mergeCell ref="E6:E7"/>
-    <mergeCell ref="J6:J7"/>
-    <mergeCell ref="F6:F7"/>
-    <mergeCell ref="M6:M7"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="J26:O26"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="A26:I26"/>
   </mergeCells>
   <phoneticPr fontId="10" type="noConversion"/>
   <printOptions horizontalCentered="1"/>
